--- a/data/trans_dic/P79$ninguna_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P79$ninguna_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,65; 95,46</t>
+          <t>89,5; 94,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,52; 95,69</t>
+          <t>91,13; 95,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91,74; 94,97</t>
+          <t>91,02; 94,19</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>87,67; 92,84</t>
+          <t>87,27; 92,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,64; 90,67</t>
+          <t>84,41; 90,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,29; 91,13</t>
+          <t>87,13; 91,09</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,36; 95,99</t>
+          <t>79,09; 85,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,07; 92,12</t>
+          <t>83,21; 91,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,21; 95,39</t>
+          <t>81,15; 86,82</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,54; 86,63</t>
+          <t>80,95; 85,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,8; 95,64</t>
+          <t>86,88; 90,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,9; 91,64</t>
+          <t>84,16; 87,46</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,06; 84,87</t>
+          <t>76,06; 83,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,62; 84,6</t>
+          <t>77,14; 82,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,35; 83,9</t>
+          <t>77,71; 81,99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,85; 96,62</t>
+          <t>83,16; 95,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78,83; 84,5</t>
+          <t>78,6; 84,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,69; 86,96</t>
+          <t>80,72; 85,9</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86,06; 90,45</t>
+          <t>84,49; 87,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>85,87; 89,82</t>
+          <t>84,44; 86,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,25; 89,12</t>
+          <t>84,81; 86,46</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>466612</t>
+          <t>503918</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>413214</t>
+          <t>447672</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>879827</t>
+          <t>951590</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>453694; 477724</t>
+          <t>487714; 514815</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>402929; 421265</t>
+          <t>437372; 457112</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>863022; 893450</t>
+          <t>932814; 965333</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>403836</t>
+          <t>430714</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>332729</t>
+          <t>366917</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>736566</t>
+          <t>797632</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>390981; 414062</t>
+          <t>415899; 442623</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>320481; 343312</t>
+          <t>353253; 378118</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>719821; 751449</t>
+          <t>779869; 815281</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>588768</t>
+          <t>380518</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>146702</t>
+          <t>163425</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>735469</t>
+          <t>543944</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>541543; 631179</t>
+          <t>364080; 395340</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>138659; 151935</t>
+          <t>154252; 170123</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>692622; 784540</t>
+          <t>524012; 560579</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>855514</t>
+          <t>926914</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>871705</t>
+          <t>735507</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1727219</t>
+          <t>1662421</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>827290; 878919</t>
+          <t>898152; 952594</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>842334; 907245</t>
+          <t>718890; 751649</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1686500; 1799144</t>
+          <t>1630226; 1694192</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>368835</t>
+          <t>428084</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>605303</t>
+          <t>636222</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>974139</t>
+          <t>1064307</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>349508; 384927</t>
+          <t>405651; 445777</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>583877; 628324</t>
+          <t>614915; 655512</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>949274; 1003661</t>
+          <t>1033878; 1090848</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>198376</t>
+          <t>192866</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>588073</t>
+          <t>648918</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>786448</t>
+          <t>841783</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>179612; 206971</t>
+          <t>176877; 202834</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>565959; 606669</t>
+          <t>626433; 670009</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>761479; 810554</t>
+          <t>815047; 867366</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2881941</t>
+          <t>2863014</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2957728</t>
+          <t>2998662</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5839669</t>
+          <t>5861676</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2828415; 2972609</t>
+          <t>2819736; 2908382</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2913566; 3047605</t>
+          <t>2959935; 3035322</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5760958; 5952717</t>
+          <t>5803718; 5916091</t>
         </is>
       </c>
     </row>
